--- a/Effect_效果表.xlsx
+++ b/Effect_效果表.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>类名</t>
   </si>
@@ -90,6 +90,15 @@
   </si>
   <si>
     <t>家族树·族人培养·节点1：族人生命 +10</t>
+  </si>
+  <si>
+    <t>W1a 验收：格位 +1（验证格位可被提升）</t>
+  </si>
+  <si>
+    <t>W1a 验收：族人信心上限 +10</t>
+  </si>
+  <si>
+    <t>W1a 验收：带出上限 +2（W3 用）</t>
   </si>
 </sst>
 </file>
@@ -135,7 +144,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -334,6 +343,66 @@
         <v>1</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="0">
+        <v>6</v>
+      </c>
+      <c r="B12" s="0">
+        <v>2</v>
+      </c>
+      <c r="C12" s="0">
+        <v>0</v>
+      </c>
+      <c r="D12" s="0">
+        <v>1</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0">
+        <v>7</v>
+      </c>
+      <c r="B13" s="0">
+        <v>4</v>
+      </c>
+      <c r="C13" s="0">
+        <v>5</v>
+      </c>
+      <c r="D13" s="0">
+        <v>10</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0">
+        <v>8</v>
+      </c>
+      <c r="B14" s="0">
+        <v>3</v>
+      </c>
+      <c r="C14" s="0">
+        <v>0</v>
+      </c>
+      <c r="D14" s="0">
+        <v>2</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/Effect_效果表.xlsx
+++ b/Effect_效果表.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>类名</t>
   </si>
@@ -99,6 +99,27 @@
   </si>
   <si>
     <t>W1a 验收：带出上限 +2（W3 用）</t>
+  </si>
+  <si>
+    <t>家族树·影响力·节点2：带出上限 +1</t>
+  </si>
+  <si>
+    <t>家族树·局外战斗·节点3：带出上限 +2</t>
+  </si>
+  <si>
+    <t>家族树·局内战斗·节点3：带出上限 +3</t>
+  </si>
+  <si>
+    <t>家族树·局外战斗·节点1：族人攻击 +5</t>
+  </si>
+  <si>
+    <t>家族树·局外战斗·节点2：族人防御 +5</t>
+  </si>
+  <si>
+    <t>家族树·局内战斗·节点1：族人速度 +2</t>
+  </si>
+  <si>
+    <t>家族树·家族产业·节点3：农田收获产量 +2</t>
   </si>
 </sst>
 </file>
@@ -144,7 +165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -403,6 +424,146 @@
         <v>1</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="0">
+        <v>9</v>
+      </c>
+      <c r="B15" s="0">
+        <v>3</v>
+      </c>
+      <c r="C15" s="0">
+        <v>0</v>
+      </c>
+      <c r="D15" s="0">
+        <v>1</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0">
+        <v>10</v>
+      </c>
+      <c r="B16" s="0">
+        <v>3</v>
+      </c>
+      <c r="C16" s="0">
+        <v>0</v>
+      </c>
+      <c r="D16" s="0">
+        <v>2</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0">
+        <v>11</v>
+      </c>
+      <c r="B17" s="0">
+        <v>3</v>
+      </c>
+      <c r="C17" s="0">
+        <v>0</v>
+      </c>
+      <c r="D17" s="0">
+        <v>3</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0">
+        <v>12</v>
+      </c>
+      <c r="B18" s="0">
+        <v>4</v>
+      </c>
+      <c r="C18" s="0">
+        <v>2</v>
+      </c>
+      <c r="D18" s="0">
+        <v>5</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0">
+        <v>13</v>
+      </c>
+      <c r="B19" s="0">
+        <v>4</v>
+      </c>
+      <c r="C19" s="0">
+        <v>3</v>
+      </c>
+      <c r="D19" s="0">
+        <v>5</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0">
+        <v>14</v>
+      </c>
+      <c r="B20" s="0">
+        <v>4</v>
+      </c>
+      <c r="C20" s="0">
+        <v>4</v>
+      </c>
+      <c r="D20" s="0">
+        <v>2</v>
+      </c>
+      <c r="E20" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0">
+        <v>15</v>
+      </c>
+      <c r="B21" s="0">
+        <v>7</v>
+      </c>
+      <c r="C21" s="0">
+        <v>2001</v>
+      </c>
+      <c r="D21" s="0">
+        <v>2</v>
+      </c>
+      <c r="E21" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>
